--- a/data/trans_orig/IP18B2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18B2-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="W122" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="U139" s="2" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="W139" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="W142" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="W143" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="W146" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -17181,7 +17181,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -17371,12 +17371,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -17386,12 +17386,12 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -17441,12 +17441,12 @@
       </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U151" s="2" t="inlineStr">
@@ -17456,12 +17456,12 @@
       </c>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -17667,12 +17667,12 @@
       </c>
       <c r="S153" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>771</t>
         </is>
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="U153" s="2" t="inlineStr">
@@ -17682,12 +17682,12 @@
       </c>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -18069,7 +18069,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U157" s="2" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="W157" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -18167,7 +18167,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -18237,7 +18237,7 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="U161" s="2" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="W161" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18958,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -19023,12 +19023,12 @@
       </c>
       <c r="S165" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U165" s="2" t="inlineStr">
@@ -19038,12 +19038,12 @@
       </c>
       <c r="V165" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W165" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -19518,12 +19518,12 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -19533,12 +19533,12 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -19553,12 +19553,12 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -19568,12 +19568,12 @@
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -19588,12 +19588,12 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
@@ -19603,12 +19603,12 @@
       </c>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -19748,12 +19748,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -19783,12 +19783,12 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -19798,12 +19798,12 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -19818,12 +19818,12 @@
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U172" s="2" t="inlineStr">
@@ -19833,12 +19833,12 @@
       </c>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U173" s="2" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="W173" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -20024,12 +20024,12 @@
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -20044,12 +20044,12 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U174" s="2" t="inlineStr">
@@ -20059,12 +20059,12 @@
       </c>
       <c r="V174" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W174" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -20353,7 +20353,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U177" s="2" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="W177" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -20441,12 +20441,12 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -20496,12 +20496,12 @@
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U178" s="2" t="inlineStr">
@@ -20511,12 +20511,12 @@
       </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W178" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -20539,12 +20539,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -20554,12 +20554,12 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -20574,12 +20574,12 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -20589,12 +20589,12 @@
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -20609,12 +20609,12 @@
       </c>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="U179" s="2" t="inlineStr">
@@ -20624,12 +20624,12 @@
       </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W179" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -20687,12 +20687,12 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
@@ -20702,12 +20702,12 @@
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="U180" s="2" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="W180" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -20835,12 +20835,12 @@
       </c>
       <c r="S181" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T181" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U181" s="2" t="inlineStr">
@@ -20850,12 +20850,12 @@
       </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W181" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="T182" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="U182" s="2" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="W182" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="T184" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U184" s="2" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="W184" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -21217,12 +21217,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -21232,12 +21232,12 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -21287,12 +21287,12 @@
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T185" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U185" s="2" t="inlineStr">
@@ -21302,12 +21302,12 @@
       </c>
       <c r="V185" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W185" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -21330,12 +21330,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -21345,12 +21345,12 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -21365,12 +21365,12 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -21380,12 +21380,12 @@
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -21400,12 +21400,12 @@
       </c>
       <c r="S186" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
@@ -21415,12 +21415,12 @@
       </c>
       <c r="V186" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W186" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="T187" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U187" s="2" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="W187" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -21631,7 +21631,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U188" s="2" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="W188" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U189" s="2" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="W189" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -21895,12 +21895,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -21910,12 +21910,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -21930,12 +21930,12 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -21965,12 +21965,12 @@
       </c>
       <c r="S191" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="T191" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U191" s="2" t="inlineStr">
@@ -21980,12 +21980,12 @@
       </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W191" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -22888,7 +22888,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -23074,12 +23074,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -23109,12 +23109,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -23222,12 +23222,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -23237,12 +23237,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -24758,7 +24758,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -24778,7 +24778,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -24941,7 +24941,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -24969,7 +24969,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -24999,12 +24999,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -25014,12 +25014,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -25034,12 +25034,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25049,12 +25049,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -26410,7 +26410,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -26925,7 +26925,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -26940,7 +26940,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -27185,12 +27185,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -27200,12 +27200,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27346,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -27381,7 +27381,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -27431,7 +27431,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -27833,7 +27833,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -27883,7 +27883,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -27946,7 +27946,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -27961,7 +27961,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -27996,7 +27996,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28624,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -28702,7 +28702,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -28787,7 +28787,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29239,7 +29239,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -29788,12 +29788,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -29803,12 +29803,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -30245,7 +30245,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -31488,7 +31488,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -31503,7 +31503,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -34477,7 +34477,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -34522,12 +34522,12 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -34542,12 +34542,12 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -34557,12 +34557,12 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -34590,7 +34590,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -34675,7 +34675,7 @@
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -34929,7 +34929,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -34999,7 +34999,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -35190,7 +35190,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -35833,7 +35833,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -35883,7 +35883,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -35898,12 +35898,12 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>755</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -35913,12 +35913,12 @@
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -36320,7 +36320,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -36335,7 +36335,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -36355,7 +36355,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
@@ -36370,7 +36370,7 @@
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -36398,7 +36398,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -36448,7 +36448,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -36468,7 +36468,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -36483,7 +36483,7 @@
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -36628,7 +36628,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -36643,7 +36643,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -36658,12 +36658,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -36673,12 +36673,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -36693,12 +36693,12 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -36708,12 +36708,12 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -36854,7 +36854,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -36869,7 +36869,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -36889,7 +36889,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -36904,7 +36904,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -36919,12 +36919,12 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -36934,12 +36934,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -37306,7 +37306,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -37321,7 +37321,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -37356,7 +37356,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -37371,12 +37371,12 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -37386,12 +37386,12 @@
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -37414,12 +37414,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -37429,12 +37429,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -37449,12 +37449,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -37464,12 +37464,12 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -37484,12 +37484,12 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -37499,12 +37499,12 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -37999,7 +37999,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -38054,7 +38054,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
@@ -38069,7 +38069,7 @@
       </c>
       <c r="W142" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -38097,7 +38097,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -38132,7 +38132,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -38147,7 +38147,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -38167,7 +38167,7 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
@@ -38182,7 +38182,7 @@
       </c>
       <c r="W143" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -38245,7 +38245,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -38260,7 +38260,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -38280,7 +38280,7 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -38295,7 +38295,7 @@
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -38775,7 +38775,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -38790,7 +38790,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -38805,12 +38805,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -38820,12 +38820,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -38840,12 +38840,12 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -38855,12 +38855,12 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -39040,7 +39040,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -39055,7 +39055,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U151" s="2" t="inlineStr">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="W151" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -39261,12 +39261,12 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -39276,12 +39276,12 @@
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -39296,12 +39296,12 @@
       </c>
       <c r="S153" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="U153" s="2" t="inlineStr">
@@ -39311,12 +39311,12 @@
       </c>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -39605,7 +39605,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -39620,7 +39620,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -39640,7 +39640,7 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="U156" s="2" t="inlineStr">
@@ -39655,7 +39655,7 @@
       </c>
       <c r="W156" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -39718,7 +39718,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -39753,7 +39753,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="U157" s="2" t="inlineStr">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="W157" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -39796,7 +39796,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -39811,7 +39811,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -39831,7 +39831,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
@@ -39876,12 +39876,12 @@
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -40022,7 +40022,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -40037,7 +40037,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -40092,7 +40092,7 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="U160" s="2" t="inlineStr">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="W160" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -40283,7 +40283,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -40298,7 +40298,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -40318,7 +40318,7 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="U162" s="2" t="inlineStr">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="W162" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -40469,12 +40469,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -40484,12 +40484,12 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -40539,12 +40539,12 @@
       </c>
       <c r="S164" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="U164" s="2" t="inlineStr">
@@ -40554,12 +40554,12 @@
       </c>
       <c r="V164" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W164" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -40587,7 +40587,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -40602,7 +40602,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -40657,7 +40657,7 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="U165" s="2" t="inlineStr">
@@ -40672,7 +40672,7 @@
       </c>
       <c r="W165" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -40848,7 +40848,7 @@
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -40863,7 +40863,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -40883,7 +40883,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U167" s="2" t="inlineStr">
@@ -40898,7 +40898,7 @@
       </c>
       <c r="W167" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -41039,7 +41039,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -41054,7 +41054,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -41074,7 +41074,7 @@
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -41109,7 +41109,7 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="U169" s="2" t="inlineStr">
@@ -41124,7 +41124,7 @@
       </c>
       <c r="W169" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -41152,7 +41152,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -41167,7 +41167,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -41182,12 +41182,12 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -41197,12 +41197,12 @@
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -41217,12 +41217,12 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
@@ -41232,12 +41232,12 @@
       </c>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -41377,12 +41377,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -41392,12 +41392,12 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -41412,12 +41412,12 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -41427,12 +41427,12 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -41447,12 +41447,12 @@
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U172" s="2" t="inlineStr">
@@ -41462,12 +41462,12 @@
       </c>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U173" s="2" t="inlineStr">
@@ -41580,7 +41580,7 @@
       </c>
       <c r="W173" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -41603,12 +41603,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -41618,12 +41618,12 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -41638,12 +41638,12 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -41653,12 +41653,12 @@
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -41673,12 +41673,12 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U174" s="2" t="inlineStr">
@@ -41688,12 +41688,12 @@
       </c>
       <c r="V174" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W174" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -41721,7 +41721,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -41791,7 +41791,7 @@
       </c>
       <c r="T175" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U175" s="2" t="inlineStr">
@@ -41806,7 +41806,7 @@
       </c>
       <c r="W175" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -41834,7 +41834,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -41849,7 +41849,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -41904,7 +41904,7 @@
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U176" s="2" t="inlineStr">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="W176" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -42017,7 +42017,7 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U177" s="2" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="W177" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -42055,12 +42055,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -42070,12 +42070,12 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -42105,7 +42105,7 @@
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
@@ -42125,12 +42125,12 @@
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="U178" s="2" t="inlineStr">
@@ -42140,12 +42140,12 @@
       </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W178" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -42183,12 +42183,12 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -42203,12 +42203,12 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -42218,12 +42218,12 @@
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -42238,12 +42238,12 @@
       </c>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="U179" s="2" t="inlineStr">
@@ -42253,12 +42253,12 @@
       </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W179" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -42356,7 +42356,7 @@
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="U180" s="2" t="inlineStr">
@@ -42371,7 +42371,7 @@
       </c>
       <c r="W180" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -42469,7 +42469,7 @@
       </c>
       <c r="T181" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U181" s="2" t="inlineStr">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="W181" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -42660,7 +42660,7 @@
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
@@ -42675,7 +42675,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -42695,7 +42695,7 @@
       </c>
       <c r="T183" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U183" s="2" t="inlineStr">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="W183" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -42738,7 +42738,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -42753,7 +42753,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="T184" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="U184" s="2" t="inlineStr">
@@ -42823,7 +42823,7 @@
       </c>
       <c r="W184" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -42846,12 +42846,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -42861,12 +42861,12 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -42886,7 +42886,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -42901,7 +42901,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -42916,12 +42916,12 @@
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T185" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="U185" s="2" t="inlineStr">
@@ -42931,12 +42931,12 @@
       </c>
       <c r="V185" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W185" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -42959,12 +42959,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -42974,12 +42974,12 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -42994,12 +42994,12 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -43009,12 +43009,12 @@
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -43029,12 +43029,12 @@
       </c>
       <c r="S186" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
@@ -43044,12 +43044,12 @@
       </c>
       <c r="V186" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W186" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -43225,7 +43225,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -43240,7 +43240,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -43260,7 +43260,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U188" s="2" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="W188" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -43338,7 +43338,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
@@ -43353,7 +43353,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -43373,7 +43373,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U189" s="2" t="inlineStr">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="W189" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -43411,12 +43411,12 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -43426,12 +43426,12 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -43451,7 +43451,7 @@
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -43481,12 +43481,12 @@
       </c>
       <c r="S190" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T190" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U190" s="2" t="inlineStr">
@@ -43496,12 +43496,12 @@
       </c>
       <c r="V190" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W190" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -43524,12 +43524,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -43539,12 +43539,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -43559,12 +43559,12 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -43574,12 +43574,12 @@
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -43594,7 +43594,7 @@
       </c>
       <c r="S191" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T191" s="2" t="inlineStr">
@@ -43609,7 +43609,7 @@
       </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W191" s="2" t="inlineStr">
@@ -44221,7 +44221,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -44236,7 +44236,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -44291,7 +44291,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -44447,7 +44447,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -44462,7 +44462,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -44517,7 +44517,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -44673,7 +44673,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -44688,7 +44688,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -44738,12 +44738,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -44753,12 +44753,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -44801,7 +44801,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -44856,7 +44856,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -45082,7 +45082,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -45097,7 +45097,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -45647,7 +45647,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -45662,7 +45662,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -45803,7 +45803,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -45818,7 +45818,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -45873,7 +45873,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -46142,7 +46142,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -46157,7 +46157,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -46212,7 +46212,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -46227,7 +46227,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -46372,7 +46372,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -46387,7 +46387,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -46407,7 +46407,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -46422,7 +46422,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -46437,12 +46437,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -46452,12 +46452,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -46628,12 +46628,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -46643,12 +46643,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -46663,12 +46663,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -46678,12 +46678,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -46972,7 +46972,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -46987,7 +46987,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -47007,7 +47007,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -47022,7 +47022,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -47163,7 +47163,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -47178,7 +47178,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -47248,7 +47248,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -47424,7 +47424,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -47439,7 +47439,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -47459,7 +47459,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -47474,7 +47474,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -47949,12 +47949,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -47964,12 +47964,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -47989,7 +47989,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -48004,7 +48004,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -48019,12 +48019,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -48034,12 +48034,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -48215,7 +48215,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -48250,7 +48250,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -48265,7 +48265,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -48328,7 +48328,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -48343,7 +48343,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -48363,7 +48363,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -48534,7 +48534,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -48554,7 +48554,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -48569,7 +48569,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -48604,7 +48604,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -48819,7 +48819,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -48834,7 +48834,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -48932,7 +48932,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -48947,7 +48947,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -49723,7 +49723,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -49738,7 +49738,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -49836,7 +49836,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -49851,7 +49851,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -50288,7 +50288,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -50303,7 +50303,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -51387,7 +51387,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -51402,7 +51402,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -51422,7 +51422,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -51613,7 +51613,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -51628,7 +51628,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -51648,7 +51648,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -51663,7 +51663,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -51874,7 +51874,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -51889,7 +51889,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -51952,7 +51952,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -51967,7 +51967,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -52002,7 +52002,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -52065,7 +52065,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -52080,7 +52080,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -52100,7 +52100,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -52115,7 +52115,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -52665,7 +52665,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -52680,7 +52680,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -52969,7 +52969,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -52984,7 +52984,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -53004,7 +53004,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -53019,7 +53019,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -53308,7 +53308,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -53323,7 +53323,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -53343,7 +53343,7 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -53358,7 +53358,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -53799,7 +53799,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -53814,7 +53814,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -54246,12 +54246,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -54261,12 +54261,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -54477,7 +54477,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -54492,7 +54492,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -54972,7 +54972,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -54987,7 +54987,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -55042,7 +55042,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -55057,7 +55057,7 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -55424,7 +55424,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -55439,7 +55439,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -55494,7 +55494,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -55509,7 +55509,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -55910,12 +55910,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -55925,12 +55925,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -55945,12 +55945,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -55960,12 +55960,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -57497,7 +57497,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -57512,7 +57512,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -57532,7 +57532,7 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -57547,7 +57547,7 @@
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -58062,7 +58062,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -58077,7 +58077,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -58092,7 +58092,7 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
@@ -58107,12 +58107,12 @@
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -58478,7 +58478,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -58493,7 +58493,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -58548,7 +58548,7 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
@@ -58563,7 +58563,7 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -60178,7 +60178,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -60193,7 +60193,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -60248,7 +60248,7 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -60263,7 +60263,7 @@
       </c>
       <c r="W147" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -60404,7 +60404,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -60419,7 +60419,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -60474,7 +60474,7 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -60489,7 +60489,7 @@
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -60629,12 +60629,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -60644,12 +60644,12 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -60699,12 +60699,12 @@
       </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U151" s="2" t="inlineStr">
@@ -60714,12 +60714,12 @@
       </c>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -60782,7 +60782,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -60797,7 +60797,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -60817,7 +60817,7 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="U152" s="2" t="inlineStr">
@@ -60832,7 +60832,7 @@
       </c>
       <c r="W152" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -60855,12 +60855,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -60870,12 +60870,12 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -60895,7 +60895,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -60910,7 +60910,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -60925,12 +60925,12 @@
       </c>
       <c r="S153" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U153" s="2" t="inlineStr">
@@ -60940,12 +60940,12 @@
       </c>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -61121,7 +61121,7 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -61136,7 +61136,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -61156,7 +61156,7 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="U155" s="2" t="inlineStr">
@@ -61171,7 +61171,7 @@
       </c>
       <c r="W155" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -61199,7 +61199,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -61214,7 +61214,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -61234,7 +61234,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -61249,7 +61249,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -61269,7 +61269,7 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="U156" s="2" t="inlineStr">
@@ -61284,7 +61284,7 @@
       </c>
       <c r="W156" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -61460,7 +61460,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -61475,7 +61475,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -61495,7 +61495,7 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
@@ -61510,7 +61510,7 @@
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -62138,7 +62138,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -62153,7 +62153,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -62173,7 +62173,7 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U164" s="2" t="inlineStr">
@@ -62188,7 +62188,7 @@
       </c>
       <c r="W164" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -62251,7 +62251,7 @@
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -62266,7 +62266,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -62286,7 +62286,7 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U165" s="2" t="inlineStr">
@@ -62301,7 +62301,7 @@
       </c>
       <c r="W165" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -62555,7 +62555,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -62570,7 +62570,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -62625,7 +62625,7 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="U168" s="2" t="inlineStr">
@@ -62640,7 +62640,7 @@
       </c>
       <c r="W168" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -62668,7 +62668,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -62683,7 +62683,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -62738,7 +62738,7 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="U169" s="2" t="inlineStr">
@@ -62753,7 +62753,7 @@
       </c>
       <c r="W169" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -62811,12 +62811,12 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -62826,12 +62826,12 @@
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -62846,12 +62846,12 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
@@ -62861,12 +62861,12 @@
       </c>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -63006,12 +63006,12 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -63021,12 +63021,12 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -63041,12 +63041,12 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -63056,12 +63056,12 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -63076,12 +63076,12 @@
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U172" s="2" t="inlineStr">
@@ -63091,12 +63091,12 @@
       </c>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -63159,7 +63159,7 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -63174,7 +63174,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -63194,7 +63194,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U173" s="2" t="inlineStr">
@@ -63209,7 +63209,7 @@
       </c>
       <c r="W173" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -63232,12 +63232,12 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -63247,12 +63247,12 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -63267,12 +63267,12 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -63282,12 +63282,12 @@
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -63302,12 +63302,12 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="U174" s="2" t="inlineStr">
@@ -63317,12 +63317,12 @@
       </c>
       <c r="V174" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W174" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -63463,7 +63463,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -63478,7 +63478,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -63498,7 +63498,7 @@
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -63513,7 +63513,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -63528,12 +63528,12 @@
       </c>
       <c r="S176" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U176" s="2" t="inlineStr">
@@ -63548,7 +63548,7 @@
       </c>
       <c r="W176" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -63576,7 +63576,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -63591,7 +63591,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -63611,7 +63611,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -63626,7 +63626,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -63641,12 +63641,12 @@
       </c>
       <c r="S177" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U177" s="2" t="inlineStr">
@@ -63656,12 +63656,12 @@
       </c>
       <c r="V177" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W177" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -63684,12 +63684,12 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -63699,12 +63699,12 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -63724,7 +63724,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
@@ -63739,7 +63739,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -63754,12 +63754,12 @@
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U178" s="2" t="inlineStr">
@@ -63769,12 +63769,12 @@
       </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W178" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -63802,7 +63802,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -63817,7 +63817,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -63832,12 +63832,12 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -63847,12 +63847,12 @@
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -63867,12 +63867,12 @@
       </c>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T179" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U179" s="2" t="inlineStr">
@@ -63882,12 +63882,12 @@
       </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W179" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -63945,12 +63945,12 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
@@ -63960,12 +63960,12 @@
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -63980,12 +63980,12 @@
       </c>
       <c r="S180" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U180" s="2" t="inlineStr">
@@ -63995,12 +63995,12 @@
       </c>
       <c r="V180" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W180" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -64028,7 +64028,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -64043,7 +64043,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -64063,7 +64063,7 @@
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
@@ -64078,7 +64078,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -64093,12 +64093,12 @@
       </c>
       <c r="S181" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T181" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U181" s="2" t="inlineStr">
@@ -64108,12 +64108,12 @@
       </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W181" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -64475,12 +64475,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -64490,12 +64490,12 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -64515,7 +64515,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -64530,7 +64530,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -64545,12 +64545,12 @@
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T185" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U185" s="2" t="inlineStr">
@@ -64560,12 +64560,12 @@
       </c>
       <c r="V185" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W185" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -64588,12 +64588,12 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -64603,12 +64603,12 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -64623,12 +64623,12 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -64638,12 +64638,12 @@
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -64658,12 +64658,12 @@
       </c>
       <c r="S186" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U186" s="2" t="inlineStr">
@@ -64673,12 +64673,12 @@
       </c>
       <c r="V186" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W186" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -64819,7 +64819,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -64834,7 +64834,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -64854,7 +64854,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -64869,7 +64869,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -64889,7 +64889,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U188" s="2" t="inlineStr">
@@ -64904,7 +64904,7 @@
       </c>
       <c r="W188" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -64927,12 +64927,12 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -64942,12 +64942,12 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -64967,7 +64967,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
@@ -64982,7 +64982,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -64997,12 +64997,12 @@
       </c>
       <c r="S189" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U189" s="2" t="inlineStr">
@@ -65012,12 +65012,12 @@
       </c>
       <c r="V189" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W189" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -65045,7 +65045,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -65060,7 +65060,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
@@ -65115,7 +65115,7 @@
       </c>
       <c r="T190" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U190" s="2" t="inlineStr">
@@ -65130,7 +65130,7 @@
       </c>
       <c r="W190" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -65153,12 +65153,12 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -65168,12 +65168,12 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -65188,12 +65188,12 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -65203,12 +65203,12 @@
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -65223,12 +65223,12 @@
       </c>
       <c r="S191" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T191" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U191" s="2" t="inlineStr">
@@ -65238,12 +65238,12 @@
       </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W191" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
